--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Salwa\Downloads\"/>
+      <ns2:absPath url="C:\Users\Salwa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A44B3DF-29CF-469A-BDEA-CB539B833A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -22,19 +22,20 @@
     <sheet name="Weekly Updates" sheetId="7" r:id="rId7"/>
     <sheet name="Activity Log" sheetId="8" r:id="rId8"/>
     <sheet name="Lists" sheetId="9" r:id="rId9"/>
+    <sheet name="Admins" sheetId="10" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns8:calcFeatures>
+        <ns8:feature name="microsoft.com:RD"/>
+        <ns8:feature name="microsoft.com:Single"/>
+        <ns8:feature name="microsoft.com:FV"/>
+        <ns8:feature name="microsoft.com:CNMTM"/>
+        <ns8:feature name="microsoft.com:LET_WF"/>
+        <ns8:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns8:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns8:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -7900,22 +7901,22 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TasksTable" displayName="TasksTable" ref="A1:N337">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" ns1:Ignorable="xr xr3" id="4" ns2:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TasksTable" displayName="TasksTable" ref="A1:N501">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Task ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Project ID"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Project"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Task Name"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Assigned To ID"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Assigned To"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Department ID"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Department"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Status"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Priority"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Due Date"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="Estimated Hours"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Actual Hours"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="Completion %"/>
+    <tableColumn id="1" ns3:uid="{00000000-0010-0000-0300-000001000000}" name="Task ID"/>
+    <tableColumn id="2" ns3:uid="{00000000-0010-0000-0300-000002000000}" name="Project ID"/>
+    <tableColumn id="3" ns3:uid="{00000000-0010-0000-0300-000003000000}" name="Project"/>
+    <tableColumn id="4" ns3:uid="{00000000-0010-0000-0300-000004000000}" name="Task Name"/>
+    <tableColumn id="5" ns3:uid="{00000000-0010-0000-0300-000005000000}" name="Assigned To ID"/>
+    <tableColumn id="6" ns3:uid="{00000000-0010-0000-0300-000006000000}" name="Assigned To"/>
+    <tableColumn id="7" ns3:uid="{00000000-0010-0000-0300-000007000000}" name="Department ID"/>
+    <tableColumn id="8" ns3:uid="{00000000-0010-0000-0300-000008000000}" name="Department"/>
+    <tableColumn id="9" ns3:uid="{00000000-0010-0000-0300-000009000000}" name="Status"/>
+    <tableColumn id="10" ns3:uid="{00000000-0010-0000-0300-00000A000000}" name="Priority"/>
+    <tableColumn id="11" ns3:uid="{00000000-0010-0000-0300-00000B000000}" name="Due Date"/>
+    <tableColumn id="12" ns3:uid="{00000000-0010-0000-0300-00000C000000}" name="Estimated Hours"/>
+    <tableColumn id="13" ns3:uid="{00000000-0010-0000-0300-00000D000000}" name="Actual Hours"/>
+    <tableColumn id="14" ns3:uid="{00000000-0010-0000-0300-00000E000000}" name="Completion %"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8529,6 +8530,80 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Basil</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>basil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dashboard Administration</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sample_data.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H15"/>
@@ -10344,38 +10419,58 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="27.6">
-      <c r="A41" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>57</v>
+      <c r="A41" t="inlineStr" s="3">
+        <is>
+          <t>E1040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="3">
+        <is>
+          <t>Abdullah Alenezi</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="3">
+        <is>
+          <t>abdullah.alenezi@example-company.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="3">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="3">
+        <is>
+          <t>Digital Products</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t>HR Specialist</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="3">
+        <is>
+          <t>Specialist</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr" s="3">
+        <is>
+          <t>Noura Alqahtani</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr" s="3">
+        <is>
+          <t>Jeddah HQ</t>
+        </is>
       </c>
       <c r="J41" s="4">
         <v>45379</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>118</v>
+      <c r="K41" t="inlineStr" s="3">
+        <is>
+          <t>Active</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:11" ht="27.6">
@@ -13327,7 +13422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O100"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
@@ -13429,32 +13524,50 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="27.6">
-      <c r="A3" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>496</v>
+      <c r="A3" t="inlineStr" s="3">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="3">
+        <is>
+          <t>Customer Mobile App Revamp</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="3">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="3">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="3">
+        <is>
+          <t>E1063</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="3">
+        <is>
+          <t>Nasser Almalki</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="3">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="3">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="3">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="J3" s="4">
         <v>46100</v>
@@ -13463,16 +13576,18 @@
         <v>46257</v>
       </c>
       <c r="L3" s="3">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M3" s="3">
-        <v>2050000</v>
+        <v>2.05e+06</v>
       </c>
       <c r="N3" s="3">
-        <v>1433944</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>493</v>
+        <v>1.43394e+06</v>
+      </c>
+      <c r="O3" t="inlineStr" s="3">
+        <is>
+          <t>Compliance</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:15" ht="27.6">
@@ -13711,32 +13826,50 @@
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>496</v>
+      <c r="A9" t="inlineStr" s="3">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="3">
+        <is>
+          <t>AI Support Assistant</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="3">
+        <is>
+          <t>D014</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="3">
+        <is>
+          <t>Corporate Training</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="3">
+        <is>
+          <t>E1122</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="3">
+        <is>
+          <t>Noura Alenezi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="3">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="3">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="3">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="J9" s="4">
         <v>46052</v>
@@ -13745,16 +13878,18 @@
         <v>46231</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M9" s="3">
-        <v>2200000</v>
+        <v>2.2e+06</v>
       </c>
       <c r="N9" s="3">
-        <v>1820428</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>500</v>
+        <v>1.82043e+06</v>
+      </c>
+      <c r="O9" t="inlineStr" s="3">
+        <is>
+          <t>Revenue Growth</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:15" ht="27.6">
@@ -14811,26 +14946,26 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="G2:G200" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="G2:G200" ns2:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Not Started,Planning,In Progress,At Risk,On Hold,Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H200" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" sqref="H2:H200" ns2:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Low,Medium,High,Critical"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I200" xr:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation type="list" sqref="I2:I200" ns2:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart ns3:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N500"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:N501"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="14" width="18" customWidth="1"/>
@@ -27185,35 +27320,55 @@
       </c>
     </row>
     <row r="285" spans="1:14" ht="27.6">
-      <c r="A285" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="E285" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F285" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G285" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H285" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I285" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J285" s="3" t="s">
-        <v>496</v>
+      <c r="A285" t="inlineStr" s="3">
+        <is>
+          <t>T0284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="3">
+        <is>
+          <t>P021</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="3">
+        <is>
+          <t>Internal Knowledge Base</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="3">
+        <is>
+          <t>Audit data model</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="3">
+        <is>
+          <t>E1075</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t>Turki Alrashid</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr" s="3">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr" s="3">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr" s="3">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr" s="3">
+        <is>
+          <t>Critical</t>
+        </is>
       </c>
       <c r="K285" s="4">
         <v>46064</v>
@@ -28833,35 +28988,55 @@
       </c>
     </row>
     <row r="323" spans="1:14" ht="41.4">
-      <c r="A323" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B323" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="C323" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="E323" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F323" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G323" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H323" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I323" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J323" s="3" t="s">
-        <v>492</v>
+      <c r="A323" t="inlineStr" s="3">
+        <is>
+          <t>T0322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="3">
+        <is>
+          <t>P024</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="3">
+        <is>
+          <t>Employee Engagement Analytics</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="3">
+        <is>
+          <t>Validate data model</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="3">
+        <is>
+          <t>E1015</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t>Mohammed Alzahrani</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr" s="3">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr" s="3">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr" s="3">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr" s="3">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="K323" s="4">
         <v>46039</v>
@@ -28873,7 +29048,7 @@
         <v>22</v>
       </c>
       <c r="N323" s="3">
-        <v>90</v>
+        <v>10</v>
       </c>
     </row>
     <row r="324" spans="1:14" ht="41.4">
@@ -29047,35 +29222,55 @@
       </c>
     </row>
     <row r="328" spans="1:14" ht="41.4">
-      <c r="A328" s="3" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B328" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="C328" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="D328" s="3" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E328" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="F328" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G328" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H328" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I328" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J328" s="3" t="s">
-        <v>496</v>
+      <c r="A328" t="inlineStr" s="3">
+        <is>
+          <t>T0327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="3">
+        <is>
+          <t>P024</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="3">
+        <is>
+          <t>Employee Engagement Analytics</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="3">
+        <is>
+          <t>Audit requirements</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="3">
+        <is>
+          <t>E1103</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="3">
+        <is>
+          <t>Abdullah Almutairi</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr" s="3">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr" s="3">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr" s="3">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr" s="3">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="K328" s="4">
         <v>46053</v>
@@ -29087,7 +29282,7 @@
         <v>8</v>
       </c>
       <c r="N328" s="3">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="329" spans="1:14" ht="41.4">
@@ -29973,18 +30168,84 @@
     <row r="500" spans="11:11">
       <c r="K500" s="5"/>
     </row>
+    <row spans="11:11" r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>T0337</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>AI Support Assistant</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>E1040</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Abdullah Alenezi</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Digital Products</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K501" s="5">
+        <v>46214</v>
+      </c>
+      <c r="L501">
+        <v>8</v>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N501">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="I2:I1000" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="I2:I1000" ns2:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Backlog,Not Started,In Progress,Blocked,In Review,Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J1000" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="list" sqref="J2:J1000" ns2:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"Low,Medium,High,Critical"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart ns3:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
